--- a/3f_v0.xlsx
+++ b/3f_v0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hmgenet\helene\projects\softwares\crewman\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2C6D3B5-50B7-431F-93D9-ED007523C76B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70057DB6-C219-47FE-9AF4-9247F0EE4AFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="1665" windowWidth="29040" windowHeight="15720" tabRatio="944" xr2:uid="{19575149-6688-42F2-88E3-84A9785EF7E3}"/>
   </bookViews>
@@ -1438,7 +1438,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="125">
+  <cellXfs count="124">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1728,10 +1728,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1815,6 +1811,9 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2238,69 +2237,69 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" s="58" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="102" t="s">
+      <c r="A1" s="100" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="103" t="s">
+      <c r="B1" s="101" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="103" t="s">
+      <c r="C1" s="101" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="103" t="s">
+      <c r="D1" s="101" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="103" t="s">
+      <c r="E1" s="101" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="104" t="s">
+      <c r="F1" s="102" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="104" t="s">
+      <c r="G1" s="102" t="s">
         <v>49</v>
       </c>
-      <c r="H1" s="105" t="s">
+      <c r="H1" s="103" t="s">
         <v>48</v>
       </c>
-      <c r="I1" s="106" t="s">
+      <c r="I1" s="104" t="s">
         <v>5</v>
       </c>
-      <c r="J1" s="103" t="s">
+      <c r="J1" s="101" t="s">
         <v>12</v>
       </c>
-      <c r="K1" s="103" t="s">
+      <c r="K1" s="101" t="s">
         <v>32</v>
       </c>
-      <c r="L1" s="103" t="s">
+      <c r="L1" s="101" t="s">
         <v>6</v>
       </c>
-      <c r="M1" s="103" t="s">
+      <c r="M1" s="101" t="s">
         <v>7</v>
       </c>
-      <c r="N1" s="103" t="s">
+      <c r="N1" s="101" t="s">
         <v>8</v>
       </c>
-      <c r="O1" s="103" t="s">
+      <c r="O1" s="101" t="s">
         <v>9</v>
       </c>
-      <c r="P1" s="103" t="s">
+      <c r="P1" s="101" t="s">
         <v>10</v>
       </c>
-      <c r="Q1" s="107" t="s">
+      <c r="Q1" s="105" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:17" s="74" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="111"/>
-      <c r="B2" s="112"/>
-      <c r="C2" s="108">
+      <c r="A2" s="109"/>
+      <c r="B2" s="110"/>
+      <c r="C2" s="106">
         <v>1</v>
       </c>
-      <c r="D2" s="112"/>
-      <c r="E2" s="112"/>
-      <c r="F2" s="113"/>
-      <c r="G2" s="114"/>
-      <c r="H2" s="112"/>
+      <c r="D2" s="110"/>
+      <c r="E2" s="110"/>
+      <c r="F2" s="111"/>
+      <c r="G2" s="112"/>
+      <c r="H2" s="110"/>
       <c r="I2" s="32">
         <v>1</v>
       </c>
@@ -2494,19 +2493,19 @@
       <c r="Q6" s="39"/>
     </row>
     <row r="7" spans="1:17" s="74" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="115" t="str">
+      <c r="A7" s="113" t="str">
         <f>IF(ISBLANK(E7),"",A$2)</f>
         <v/>
       </c>
-      <c r="B7" s="116"/>
-      <c r="C7" s="109">
+      <c r="B7" s="114"/>
+      <c r="C7" s="107">
         <v>2</v>
       </c>
-      <c r="D7" s="116"/>
-      <c r="E7" s="116"/>
-      <c r="F7" s="117"/>
-      <c r="G7" s="116"/>
-      <c r="H7" s="118"/>
+      <c r="D7" s="114"/>
+      <c r="E7" s="114"/>
+      <c r="F7" s="115"/>
+      <c r="G7" s="114"/>
+      <c r="H7" s="116"/>
       <c r="I7" s="40">
         <v>1</v>
       </c>
@@ -2700,19 +2699,19 @@
       <c r="Q11" s="48"/>
     </row>
     <row r="12" spans="1:17" s="74" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="111" t="str">
+      <c r="A12" s="109" t="str">
         <f>IF(ISBLANK(E12),"",A$2)</f>
         <v/>
       </c>
-      <c r="B12" s="112"/>
-      <c r="C12" s="108">
+      <c r="B12" s="110"/>
+      <c r="C12" s="106">
         <v>3</v>
       </c>
-      <c r="D12" s="112"/>
-      <c r="E12" s="112"/>
-      <c r="F12" s="113"/>
-      <c r="G12" s="119"/>
-      <c r="H12" s="112"/>
+      <c r="D12" s="110"/>
+      <c r="E12" s="110"/>
+      <c r="F12" s="111"/>
+      <c r="G12" s="117"/>
+      <c r="H12" s="110"/>
       <c r="I12" s="32">
         <v>1</v>
       </c>
@@ -2906,19 +2905,19 @@
       <c r="Q16" s="39"/>
     </row>
     <row r="17" spans="1:17" s="74" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="120" t="str">
+      <c r="A17" s="118" t="str">
         <f>IF(ISBLANK(E17),"",A$2)</f>
         <v/>
       </c>
-      <c r="B17" s="121"/>
-      <c r="C17" s="110">
+      <c r="B17" s="119"/>
+      <c r="C17" s="108">
         <v>4</v>
       </c>
-      <c r="D17" s="121"/>
-      <c r="E17" s="121"/>
-      <c r="F17" s="122"/>
-      <c r="G17" s="117"/>
-      <c r="H17" s="118"/>
+      <c r="D17" s="119"/>
+      <c r="E17" s="119"/>
+      <c r="F17" s="120"/>
+      <c r="G17" s="115"/>
+      <c r="H17" s="116"/>
       <c r="I17" s="40">
         <v>1</v>
       </c>
@@ -3112,19 +3111,19 @@
       <c r="Q21" s="48"/>
     </row>
     <row r="22" spans="1:17" s="74" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="111" t="str">
+      <c r="A22" s="109" t="str">
         <f>IF(ISBLANK(E22),"",A$2)</f>
         <v/>
       </c>
-      <c r="B22" s="112"/>
-      <c r="C22" s="108">
+      <c r="B22" s="110"/>
+      <c r="C22" s="106">
         <v>5</v>
       </c>
-      <c r="D22" s="112"/>
-      <c r="E22" s="112"/>
-      <c r="F22" s="113"/>
-      <c r="G22" s="119"/>
-      <c r="H22" s="112"/>
+      <c r="D22" s="110"/>
+      <c r="E22" s="110"/>
+      <c r="F22" s="111"/>
+      <c r="G22" s="117"/>
+      <c r="H22" s="110"/>
       <c r="I22" s="32">
         <v>1</v>
       </c>
@@ -3322,15 +3321,15 @@
         <f>IF(ISBLANK(E27),"",A$2)</f>
         <v/>
       </c>
-      <c r="B27" s="121"/>
-      <c r="C27" s="110">
+      <c r="B27" s="119"/>
+      <c r="C27" s="108">
         <v>6</v>
       </c>
-      <c r="D27" s="121"/>
-      <c r="E27" s="121"/>
-      <c r="F27" s="122"/>
-      <c r="G27" s="117"/>
-      <c r="H27" s="118"/>
+      <c r="D27" s="119"/>
+      <c r="E27" s="119"/>
+      <c r="F27" s="120"/>
+      <c r="G27" s="115"/>
+      <c r="H27" s="116"/>
       <c r="I27" s="40">
         <v>1</v>
       </c>
@@ -3524,16 +3523,16 @@
       <c r="Q31" s="48"/>
     </row>
     <row r="32" spans="1:17" s="74" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="111"/>
-      <c r="B32" s="112"/>
-      <c r="C32" s="108">
+      <c r="A32" s="109"/>
+      <c r="B32" s="110"/>
+      <c r="C32" s="106">
         <v>7</v>
       </c>
-      <c r="D32" s="112"/>
-      <c r="E32" s="112"/>
-      <c r="F32" s="113"/>
-      <c r="G32" s="123"/>
-      <c r="H32" s="124"/>
+      <c r="D32" s="110"/>
+      <c r="E32" s="110"/>
+      <c r="F32" s="111"/>
+      <c r="G32" s="121"/>
+      <c r="H32" s="122"/>
       <c r="I32" s="32">
         <v>1</v>
       </c>
@@ -3727,19 +3726,19 @@
       <c r="Q36" s="39"/>
     </row>
     <row r="37" spans="1:17" s="74" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="120" t="str">
+      <c r="A37" s="118" t="str">
         <f>IF(ISBLANK(E37),"",A$2)</f>
         <v/>
       </c>
-      <c r="B37" s="121"/>
-      <c r="C37" s="110">
+      <c r="B37" s="119"/>
+      <c r="C37" s="108">
         <v>8</v>
       </c>
-      <c r="D37" s="121"/>
-      <c r="E37" s="121"/>
-      <c r="F37" s="122"/>
-      <c r="G37" s="117"/>
-      <c r="H37" s="118"/>
+      <c r="D37" s="119"/>
+      <c r="E37" s="119"/>
+      <c r="F37" s="120"/>
+      <c r="G37" s="115"/>
+      <c r="H37" s="116"/>
       <c r="I37" s="40">
         <v>1</v>
       </c>
@@ -3933,19 +3932,19 @@
       <c r="Q41" s="48"/>
     </row>
     <row r="42" spans="1:17" s="74" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="111" t="str">
+      <c r="A42" s="109" t="str">
         <f>IF(ISBLANK(E42),"",A$2)</f>
         <v/>
       </c>
-      <c r="B42" s="112"/>
-      <c r="C42" s="108">
+      <c r="B42" s="110"/>
+      <c r="C42" s="106">
         <v>9</v>
       </c>
-      <c r="D42" s="112"/>
-      <c r="E42" s="112"/>
-      <c r="F42" s="113"/>
-      <c r="G42" s="119"/>
-      <c r="H42" s="112"/>
+      <c r="D42" s="110"/>
+      <c r="E42" s="110"/>
+      <c r="F42" s="111"/>
+      <c r="G42" s="117"/>
+      <c r="H42" s="110"/>
       <c r="I42" s="32">
         <v>1</v>
       </c>
@@ -4139,19 +4138,19 @@
       <c r="Q46" s="39"/>
     </row>
     <row r="47" spans="1:17" s="74" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="120" t="str">
+      <c r="A47" s="118" t="str">
         <f>IF(ISBLANK(E47),"",A$2)</f>
         <v/>
       </c>
-      <c r="B47" s="121"/>
-      <c r="C47" s="110">
+      <c r="B47" s="119"/>
+      <c r="C47" s="108">
         <v>10</v>
       </c>
-      <c r="D47" s="121"/>
-      <c r="E47" s="121"/>
-      <c r="F47" s="122"/>
-      <c r="G47" s="117"/>
-      <c r="H47" s="118"/>
+      <c r="D47" s="119"/>
+      <c r="E47" s="119"/>
+      <c r="F47" s="120"/>
+      <c r="G47" s="115"/>
+      <c r="H47" s="116"/>
       <c r="I47" s="40">
         <v>1</v>
       </c>
@@ -4345,6 +4344,7 @@
       <c r="Q51" s="52"/>
     </row>
   </sheetData>
+  <sheetProtection algorithmName="SHA-512" hashValue="3Y4qOsC4DTyGVm/BiUs/kwG7mqYv6UzHEY7fvkxwpLXapJdgCKmWydRUpZKVM2/jbZBns2R6YD0s0kNiSlelRQ==" saltValue="4ZANhsJUHULzorSA69POZg==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
@@ -4419,13 +4419,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A1" s="101" t="s">
+      <c r="A1" s="99" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="101" t="s">
+      <c r="B1" s="99" t="s">
         <v>28</v>
       </c>
-      <c r="C1" s="101" t="s">
+      <c r="C1" s="99" t="s">
         <v>50</v>
       </c>
       <c r="I1" s="98" t="s">
@@ -4437,7 +4437,7 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="71"/>
-      <c r="B2" s="100" t="str">
+      <c r="B2" s="1" t="str">
         <f>_xlfn.XLOOKUP(A2,$I$2:$I$8,$J$2:$J$8,"")</f>
         <v/>
       </c>
@@ -4451,7 +4451,7 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="71"/>
-      <c r="B3" s="100" t="str">
+      <c r="B3" s="1" t="str">
         <f>_xlfn.XLOOKUP(A3,$I$2:$I$8,$J$2:$J$8,"")</f>
         <v/>
       </c>
@@ -4465,8 +4465,8 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="71"/>
-      <c r="B4" s="100" t="str">
-        <f t="shared" ref="B3:B41" si="0">_xlfn.XLOOKUP(A4,$I$2:$I$8,$J$2:$J$8,"")</f>
+      <c r="B4" s="1" t="str">
+        <f t="shared" ref="B4:B41" si="0">_xlfn.XLOOKUP(A4,$I$2:$I$8,$J$2:$J$8,"")</f>
         <v/>
       </c>
       <c r="C4" s="71"/>
@@ -4479,7 +4479,7 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="71"/>
-      <c r="B5" s="100" t="str">
+      <c r="B5" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -4493,7 +4493,7 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="71"/>
-      <c r="B6" s="100" t="str">
+      <c r="B6" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -4507,7 +4507,7 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="71"/>
-      <c r="B7" s="100" t="str">
+      <c r="B7" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -4521,7 +4521,7 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="71"/>
-      <c r="B8" s="100" t="str">
+      <c r="B8" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -4535,7 +4535,7 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="71"/>
-      <c r="B9" s="100" t="str">
+      <c r="B9" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -4543,7 +4543,7 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="71"/>
-      <c r="B10" s="100" t="str">
+      <c r="B10" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -4551,7 +4551,7 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="71"/>
-      <c r="B11" s="100" t="str">
+      <c r="B11" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -4559,7 +4559,7 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="71"/>
-      <c r="B12" s="100" t="str">
+      <c r="B12" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -4567,7 +4567,7 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="71"/>
-      <c r="B13" s="100" t="str">
+      <c r="B13" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -4575,7 +4575,7 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="71"/>
-      <c r="B14" s="100" t="str">
+      <c r="B14" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -4583,7 +4583,7 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" s="71"/>
-      <c r="B15" s="100" t="str">
+      <c r="B15" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -4591,7 +4591,7 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" s="71"/>
-      <c r="B16" s="100" t="str">
+      <c r="B16" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -4599,7 +4599,7 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="71"/>
-      <c r="B17" s="100" t="str">
+      <c r="B17" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -4607,7 +4607,7 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" s="71"/>
-      <c r="B18" s="100" t="str">
+      <c r="B18" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -4615,7 +4615,7 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" s="71"/>
-      <c r="B19" s="100" t="str">
+      <c r="B19" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -4623,7 +4623,7 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" s="71"/>
-      <c r="B20" s="100" t="str">
+      <c r="B20" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -4631,7 +4631,7 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" s="71"/>
-      <c r="B21" s="100" t="str">
+      <c r="B21" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -4639,7 +4639,7 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" s="71"/>
-      <c r="B22" s="100" t="str">
+      <c r="B22" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -4647,7 +4647,7 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" s="71"/>
-      <c r="B23" s="100" t="str">
+      <c r="B23" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -4655,7 +4655,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" s="71"/>
-      <c r="B24" s="100" t="str">
+      <c r="B24" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -4663,7 +4663,7 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" s="71"/>
-      <c r="B25" s="100" t="str">
+      <c r="B25" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -4671,7 +4671,7 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" s="71"/>
-      <c r="B26" s="100" t="str">
+      <c r="B26" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -4679,7 +4679,7 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" s="71"/>
-      <c r="B27" s="100" t="str">
+      <c r="B27" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -4687,7 +4687,7 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" s="71"/>
-      <c r="B28" s="100" t="str">
+      <c r="B28" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -4695,7 +4695,7 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" s="71"/>
-      <c r="B29" s="100" t="str">
+      <c r="B29" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -4703,7 +4703,7 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" s="71"/>
-      <c r="B30" s="100" t="str">
+      <c r="B30" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -4711,7 +4711,7 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" s="71"/>
-      <c r="B31" s="100" t="str">
+      <c r="B31" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -4719,7 +4719,7 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" s="71"/>
-      <c r="B32" s="100" t="str">
+      <c r="B32" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -4727,7 +4727,7 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" s="71"/>
-      <c r="B33" s="100" t="str">
+      <c r="B33" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -4735,7 +4735,7 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" s="71"/>
-      <c r="B34" s="100" t="str">
+      <c r="B34" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -4743,7 +4743,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" s="71"/>
-      <c r="B35" s="100" t="str">
+      <c r="B35" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -4751,7 +4751,7 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" s="71"/>
-      <c r="B36" s="100" t="str">
+      <c r="B36" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -4759,7 +4759,7 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" s="71"/>
-      <c r="B37" s="100" t="str">
+      <c r="B37" s="1" t="str">
         <f>_xlfn.XLOOKUP(A37,$I$2:$I$8,$J$2:$J$8,"")</f>
         <v/>
       </c>
@@ -4767,7 +4767,7 @@
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" s="71"/>
-      <c r="B38" s="100" t="str">
+      <c r="B38" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -4775,7 +4775,7 @@
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" s="71"/>
-      <c r="B39" s="100" t="str">
+      <c r="B39" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -4783,7 +4783,7 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" s="71"/>
-      <c r="B40" s="100" t="str">
+      <c r="B40" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -4791,7 +4791,7 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" s="71"/>
-      <c r="B41" s="100" t="str">
+      <c r="B41" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -4821,10 +4821,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" s="101" t="s">
+      <c r="A1" s="99" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="101" t="s">
+      <c r="B1" s="99" t="s">
         <v>34</v>
       </c>
     </row>
@@ -4895,19 +4895,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="19.8" x14ac:dyDescent="0.3">
-      <c r="A1" s="99" t="str">
+      <c r="A1" s="123" t="str">
         <f>_xlfn.CONCAT("Schedule for ",Flight_inventory!A2)</f>
         <v xml:space="preserve">Schedule for </v>
       </c>
-      <c r="B1" s="99"/>
-      <c r="C1" s="99"/>
-      <c r="D1" s="99"/>
-      <c r="E1" s="99"/>
-      <c r="F1" s="99"/>
-      <c r="G1" s="99"/>
-      <c r="H1" s="99"/>
-      <c r="I1" s="99"/>
-      <c r="J1" s="99"/>
+      <c r="B1" s="123"/>
+      <c r="C1" s="123"/>
+      <c r="D1" s="123"/>
+      <c r="E1" s="123"/>
+      <c r="F1" s="123"/>
+      <c r="G1" s="123"/>
+      <c r="H1" s="123"/>
+      <c r="I1" s="123"/>
+      <c r="J1" s="123"/>
       <c r="K1" s="29"/>
     </row>
     <row r="3" spans="1:11" ht="27.6" x14ac:dyDescent="0.3">
@@ -6440,12 +6440,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="19.8" x14ac:dyDescent="0.3">
-      <c r="A1" s="99" t="str">
+      <c r="A1" s="123" t="str">
         <f>_xlfn.CONCAT("Manifest for ",Flight_inventory!A2)</f>
         <v xml:space="preserve">Manifest for </v>
       </c>
-      <c r="B1" s="99"/>
-      <c r="C1" s="99"/>
+      <c r="B1" s="123"/>
+      <c r="C1" s="123"/>
     </row>
     <row r="3" spans="1:3" s="54" customFormat="1" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="53" t="e" cm="1" vm="1">
@@ -6953,6 +6953,7 @@
       <c r="C131" s="70"/>
     </row>
   </sheetData>
+  <sheetProtection algorithmName="SHA-512" hashValue="1YOOBHOhjFkXC5v93GzF6R3/HClAY9xoO2nX6VFPe76eqGkgAVTQTiAW1zel9CJVDlGB77U3BVaDIVk5jnE1QA==" saltValue="4LAR6S0JUtL35M2f/CV4Nw==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A1:C1"/>
   </mergeCells>
@@ -6983,47 +6984,47 @@
     <col min="14" max="14" width="14.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:14" s="10" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="99" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="99" t="s">
         <v>35</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="99" t="s">
         <v>16</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="99" t="s">
         <v>17</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="99" t="s">
         <v>18</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="99" t="s">
         <v>19</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="99" t="s">
         <v>20</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="99" t="s">
         <v>36</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="99" t="s">
         <v>21</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="99" t="s">
         <v>22</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="99" t="s">
         <v>26</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="99" t="s">
         <v>27</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="99" t="s">
         <v>25</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" s="99" t="s">
         <v>24</v>
       </c>
     </row>
@@ -11828,7 +11829,7 @@
       <c r="N301" s="71"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="jBjJ/Mm2pF4dxSa5OhXh4uBr5+Okr7zBTT2dnhJnYKoWetN63QElzzRumbCaQQL9+W59LIsfuCqC1L65GTb6JQ==" saltValue="Y7TKrj2wau3ew9YgggK4QQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="f0ByW0xDX8iWIFI/4oJN2QXU8AaalRpaZlfNiEOKTZOzJw2ndbAZuJ4Y+MEfaYvrLm4xFjbROXeRzgZcS1ozCw==" saltValue="tXx446OQDBzLt1N9zrv7mg==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -11847,14 +11848,14 @@
     <col min="3" max="3" width="28.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:3" s="10" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="99" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="99" t="s">
         <v>37</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="99" t="s">
         <v>38</v>
       </c>
     </row>
@@ -11909,7 +11910,7 @@
       <c r="C11" s="71"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="TOT5BRj9zWgwK7Rd6x2O6ns2M1Hn05HM7h/wWThT+wkSJpptHf4OGtRZEVVOuPxOEOepA4MmvCLh0c6nRbC1AQ==" saltValue="bugK4du5oVt2mi96WdQa4A==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="rpHsOx7DfBRsLv6oRdjRuduLvqaZyII34/Jnbl37WVgFnmnYWmb+NESqbMfDXmlNJXxXY5d3XSditTRUtPZPfQ==" saltValue="9/dKrhp325m1k8npizLA5Q==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -11927,10 +11928,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="99" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="99" t="s">
         <v>50</v>
       </c>
     </row>
@@ -12055,6 +12056,7 @@
       <c r="B31" s="71"/>
     </row>
   </sheetData>
+  <sheetProtection algorithmName="SHA-512" hashValue="Xk2/gm6Hf2bwdzq1vKveYYZeB6t3oMltG9hE3FlRKwoI/gqWIgmLVaexbgIfVWMCOU8Zw8bhhhPVhqFvTpcozA==" saltValue="J4cmgTRNx8gasPgytuC/zA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -12072,10 +12074,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="99" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="99" t="s">
         <v>50</v>
       </c>
     </row>
@@ -12200,7 +12202,7 @@
       <c r="B31" s="71"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="10pHAH78iedwkPQHw1De8ISrENy7iMKoSGSBXTg3lr8og89qEuycFU5bpnLaSSAaVUxYu585TimxKXtDnBoZ2w==" saltValue="lXu9zL2qWPU06GxOWm9x0g==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="7zSWTqSeOzMZyf1vn3Rm/VrsKzMqiGgz33kOGnjEempaGZ71kM7zpF/xXIZFInTkhKJkf/MkQfzkArnUrMJRQQ==" saltValue="iyaErTgaXOeqZuHpoTl79g==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -12219,7 +12221,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="99" t="s">
         <v>13</v>
       </c>
       <c r="D1" s="96" t="s">
@@ -12282,7 +12284,7 @@
       <c r="G13" s="2"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="YROf0GUZyEy5KQdRyV7CNUUTwiOThNrq+vr/W5N1wo+tbqUBsU4UFu3rT4LqDI1wgqRDA9dJ/xHQXTl3hLE2Ag==" saltValue="wVSnNbXkryzpNw/D+mO8IA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="0n50+GPpOIaFWeN9XPEfZHn8wUwz9h2DDpHy+pk8b8PvYJN/nXUc4vbRFnJ2Byp2DRCLZUVXjAJMvgdxVP4Q6w==" saltValue="uggt2ffHSV81TTxqM+8JQg==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A11" xr:uid="{0B8B46E4-15A1-47FA-AC88-0CBCA1D3E025}">
       <formula1>_xlfn.ANCHORARRAY($G$2)</formula1>
@@ -12304,10 +12306,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" s="101" t="s">
+      <c r="A1" s="99" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="101" t="s">
+      <c r="B1" s="99" t="s">
         <v>50</v>
       </c>
     </row>
